--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0035.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0035.xlsx
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Lát cắt tiếp theo sắp đến rồi. Ta biết ngươi có hàng tá câu hỏi, nhưng khoan đã. Cứ theo ta đã.</t>
+          <t>Lát cắt tiếp theo sắp đến rồi. Tao biết mày có hàng tá câu hỏi, nhưng khoan đã. Cứ theo tao đã.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Thở đều... Không có dấu hiệu kết tinh Irideglow. Có thể loại trừ khả năng {Male=hắn;Female=cô ta} là một trong những Kẻ Bị Bỏ Lại.</t>
+          <t>Thở đều... Không có dấu hiệu kết tinh Irideglow. Có thể loại trừ khả năng {Male=he;Female=she} là một trong những Kẻ Bị Bỏ Lại.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>À, Chisa, lúc nào cũng nghiêm túc thế. Ta thấy {Male=hắn;Female=cô ấy} trông là người tốt đấy.</t>
+          <t>À, Chisa, lúc nào cũng nghiêm túc thế. Tao thấy {Male=he;Female=she} trông là người tốt đấy.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Một vết rách xuất hiện. Một bàn tay thò ra từ đó và kéo ta vào.</t>
+          <t>Một vết rách xuất hiện. Một bàn tay thò ra từ đó và kéo tao vào.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Lần đầu ta tìm thấy nó, bên trong bừa bộn không chịu nổi. Ta đã mất hai tháng để dọn dẹp. Giờ thì vẫn chưa gọn gàng lắm, nhưng đủ để nghỉ ngơi và trú ẩn rồi.</t>
+          <t>Lần đầu tao tìm thấy nó, bên trong bừa bộn không chịu nổi. Tao đã mất hai tháng để dọn dẹp. Giờ thì vẫn chưa gọn gàng lắm, nhưng đủ để nghỉ ngơi và trú ẩn rồi.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Nó biết rõ bố cục thành phố và hệ thống giao thông hơn ai hết. Nó đã giúp ta rất nhiều. Nhưng tất cả những gì ta có thể trả ơn chỉ là vài ly cà phê và chút đồ tráng miệng.</t>
+          <t>Nó biết rõ bố cục thành phố và hệ thống giao thông hơn ai hết. Nó đã giúp tao rất nhiều. Nhưng tất cả những gì tao có thể trả ơn chỉ là vài ly cà phê và chút đồ tráng miệng.</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Trong lúc đó, Triển lãm Mùa hè Geiei Thư viện đang diễn ra sôi nổi tại Phố Ngầm Hanakage. Những cuộn băng video cổ hiếm có mặt tại đây, mời gọi bạn thong thả dạo bước qua dòng sông dài của lịch sử.</t>
+          <t>Trong lúc đó, Triển lãm Mùa hè Geiei Gallery đang diễn ra sôi nổi tại Phố Ngầm Hanakage. Những cuộn băng video cổ hiếm có mặt tại đây, mời gọi bạn thong thả dạo bước qua dòng sông dài của lịch sử.</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Có gì cậu cần giúp không, hành khách?</t>
+          <t>Có gì bạn cần giúp không, hành khách?</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Ta muốn tìm hiểu về thành phố này.</t>
+          <t>Tao muốn tìm hiểu về thành phố này.</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Ta muốn tìm hiểu về ngươi.</t>
+          <t>Tao muốn tìm hiểu về mày.</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Ta à? Ta là Namipon! Một chú nhóc lang thang khắp thành phố, sửa chữa linh tinh đây đó. Ta cũng có thể giúp cậu tìm đường đấy.</t>
+          <t>Tao à? Tao là Namipon! Một chú nhóc lang thang khắp thành phố, sửa chữa linh tinh đây đó. Tao cũng có thể giúp cậu tìm đường đấy.</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Ừ! Mọi thứ ở quán &lt;ano=Train Conductor&gt;Shashou&lt;/ano&gt; này đều do tôi quản lý đấy! Cậu có muốn thử một tách đặc sản nhà mới pha không?</t>
+          <t>Ừ! Mọi thứ ở quán &lt;ano=Train Conductor&gt;Shashou&lt;/ano&gt; này đều do tôi quản lý đấy! bạn có muốn thử một tách đặc sản nhà mới pha không?</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao thế?</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Ta nghi ngờ chúng không còn thực sự sống nữa. Chỉ là... những Dư Âm còn sót lại thôi. Ta gọi chúng là &lt;te href=851065&gt;Left Behind&lt;/te&gt;.</t>
+          <t>Ta nghi ngờ chúng không còn thực sự sống nữa. Chỉ là... những Dư Âm còn sót lại thôi. Ta gọi chúng là &lt;te href=851065&gt;Những Kẻ Bị Bỏ Lại&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Nhưng điều chúng ta biết là: Sau Lament, Namipon có được hình hài và ý chí riêng. Là linh vật của Honami, nó biết thành phố như lòng bàn tay. Cấu trúc, lối đi. Ta tin nó là một đồng đội đáng tin cậy.</t>
+          <t>Nhưng điều chúng ta biết là: Sau Lament, Namipon có được hình hài và ý chí riêng. Là linh vật của Honami, nó biết thành phố như lòng bàn tay. Cấu trúc, lối đi. Tao tin nó là một đồng đội đáng tin cậy.</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Ta đi quanh xem xét chút được không?</t>
+          <t>Tao đi quanh xem xét chút được không?</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Bên trong Sonoro này, thời gian và không gian đều mong manh. Với đủ Năng Lượng Cộng Hưởng, ta có thể lần theo "sợi dây" của chúng và cắt đứt chúng.</t>
+          <t>Bên trong Sonoro này, thời gian và không gian đều mong manh. Với đủ Resonance Energy, ta có thể lần theo "sợi dây" của chúng và cắt đứt chúng.</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Đó là cách ta đã làm lúc nãy. Ta cắt qua những khoảng trống không gian để đưa ngươi đến gần căn cứ.</t>
+          <t>Đó là cách tao đã làm lúc nãy. Tao cắt qua những khoảng trống không gian để đưa mày đến gần căn cứ.</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Chisa và Namipon kể cho cậu nghe về lịch sử Thành phố Honami. Dù Lament đã biến nơi này thành đống đổ nát từ hàng chục năm trước, những hậu quả kéo dài của nó cũng đã phong ấn thành phố bên trong một Quả Cầu Sonoro. Thời gian ở đây như bị đóng băng vào khoảnh khắc Lament ập đến, nhốt cả thành phố trong vòng lặp vô tận của những giây phút cuối cùng. Quán cà phê nơi cậu đang đứng chính là khu vực an toàn mà Chisa tạo ra bằng Forte "cắt gọt" của mình.</t>
+          <t>Chisa và Namipon kể cho cậu nghe về lịch sử Thành phố Honami. Dù Lament đã biến nơi này thành đống đổ nát từ hàng chục năm trước, những hậu quả kéo dài của nó cũng đã phong ấn thành phố bên trong một Sonoro Sphere. Thời gian ở đây như bị đóng băng vào khoảnh khắc Lament ập đến, nhốt cả thành phố trong vòng lặp vô tận của những giây phút cuối cùng. Quán cà phê nơi cậu đang đứng chính là khu vực an toàn mà Chisa tạo ra bằng Forte "cắt gọt" của mình.</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Kẻ đã kéo ta vào cái Sonoro này đeo một cái đồng hồ giống thế.</t>
+          <t>Kẻ đã kéo tao vào cái Sonoro này đeo một cái đồng hồ giống thế.</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Sau đó, ta rời căn cứ cũ và đến đây, với hy vọng tìm thấy cô ấy. Ta vẫn cố liên lạc với Tháp... nhưng lần nào cũng thất bại. Ở rìa Lament, không gian bị xé toạc. Cảm giác như gần hơn, nhưng thực ra chẳng gần chút nào.</t>
+          <t>Sau đó, tao rời căn cứ cũ và đến đây, với hy vọng tìm thấy cô ấy. Tao vẫn cố liên lạc với Tháp... nhưng lần nào cũng thất bại. Ở rìa Lament, không gian bị xé toạc. Cảm giác như gần hơn, nhưng thực ra chẳng gần chút nào.</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Như thế này! Những &lt;te href=851067&gt;Longings&lt;/te&gt; từ &lt;ano=Human Reverberations&gt;Dấu Vết Còn Lại&lt;/ano&gt; của Honami. Chính chúng đã đánh thức ta, và sẽ dẫn đường cho chúng ta đến Tháp.</t>
+          <t>Như thế này! Những &lt;te href=851067&gt;Khát Vọng&lt;/te&gt; từ &lt;ano=Human Reverberations&gt;Dấu Vết Còn Lại&lt;/ano&gt; của Honami. Chính chúng đã đánh thức ta, và sẽ dẫn đường cho chúng ta đến Tháp.</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Tính cả ta. Càng đông càng nhanh xong việc.</t>
+          <t>Tính cả tao. Càng đông càng nhanh xong việc.</t>
         </is>
       </c>
     </row>
@@ -15981,7 +15981,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Tiếng vọng của Niềm Khát Khao. Khi quá nhiều tiếng vọng ùa về cùng lúc, đầu óc cậu như bị ai đó bấm nút tua lại vậy.</t>
+          <t>Echo của Niềm Khát Khao. Khi quá nhiều Echo ùa về cùng lúc, đầu óc cậu như bị ai đó bấm nút tua lại vậy.</t>
         </is>
       </c>
     </row>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Đây là loại thuốc tác dụng nhanh tốt nhất ta có. Chắc lát nữa sẽ đỡ thôi.</t>
+          <t>Đây là loại thuốc tác dụng nhanh tốt nhất tao có. Chắc lát nữa sẽ đỡ thôi.</t>
         </is>
       </c>
     </row>
@@ -21636,7 +21636,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Thì ra trong thành phố vẫn còn những người bình thường khác... Ta cứ tưởng chỉ có bọn Ve Sầu Đỏ ở quê ta mới thích di chuyển theo đàn thế. Không ngờ ở đây cũng có loại tương tự.</t>
+          <t>Thì ra trong thành phố vẫn còn những người bình thường khác... Tao cứ tưởng chỉ có bọn Ve Sầu Đỏ ở quê tao mới thích di chuyển theo đàn thế. Không ngờ ở đây cũng có loại tương tự.</t>
         </is>
       </c>
     </row>
@@ -21896,7 +21896,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Ta không thể hiểu nổi phương pháp của họ qua mấy cái hồ sơ này, nhưng rõ ràng có gì đó rất sai trái.</t>
+          <t>Tao không thể hiểu nổi phương pháp của họ qua mấy cái hồ sơ này, nhưng rõ ràng có gì đó rất sai trái.</t>
         </is>
       </c>
     </row>
@@ -24561,7 +24561,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Bọn mặc áo đỏ lén lút sửa chữa lung tung mỗi ngày... Đánh dấu lời ta đi, chúng chắc chắn đang mưu đồ gì đó không tốt!</t>
+          <t>Bọn mặc áo đỏ lén lút sửa chữa lung tung mỗi ngày... Đánh dấu lời tao đi, chúng chắc chắn đang mưu đồ gì đó không tốt!</t>
         </is>
       </c>
     </row>
@@ -27161,7 +27161,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Không tệ.</t>
+          <t>Khá đấy.</t>
         </is>
       </c>
     </row>
@@ -27681,7 +27681,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Ta sẽ thử xem sao!</t>
+          <t>Tao sẽ thử xem sao!</t>
         </is>
       </c>
     </row>
@@ -32036,7 +32036,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao thế?</t>
         </is>
       </c>
     </row>
